--- a/Administracion/Lista_Asistencia_ASS_CRN236396.xlsx
+++ b/Administracion/Lista_Asistencia_ASS_CRN236396.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ddf5fb2bc65e958/Documentos/GitHub/lc_arquitectura_de_sistemas_de_seguridad/Administracion/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\OneDrive\Documentos\GitHub\lc_arquitectura_de_sistemas_de_seguridad\Administracion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="14_{545CCF96-C524-4C47-965E-B405D4770607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56960807-9F25-4073-AF78-1FEDF67E0AE4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38376A8-59C5-44D7-8BA9-AC04E8A4A2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="308">
   <si>
     <t>LISTA DE ASISTENCIA — ARQUITECTURA DE SISTEMAS DE SEGURIDAD  |  Ciclo 2026-A  |  CRN 236396  |  Sección 401  |  Aula 101 Edif. 4L</t>
   </si>
@@ -999,6 +999,9 @@
   </si>
   <si>
     <t>DE LUNA MOZQUEDA EMMANUEL</t>
+  </si>
+  <si>
+    <t>Puntos Extra Presentacion</t>
   </si>
 </sst>
 </file>
@@ -1518,10 +1521,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1723,25 +1722,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO35"/>
+  <dimension ref="A1:AP35"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="17" width="4.42578125" customWidth="1"/>
-    <col min="18" max="18" width="7" customWidth="1"/>
-    <col min="19" max="32" width="4.42578125" customWidth="1"/>
-    <col min="33" max="33" width="4.42578125" style="26" customWidth="1"/>
-    <col min="34" max="38" width="4.42578125" customWidth="1"/>
-    <col min="39" max="40" width="7" customWidth="1"/>
-    <col min="41" max="41" width="9" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="8" max="18" width="4.42578125" customWidth="1"/>
+    <col min="19" max="19" width="7" customWidth="1"/>
+    <col min="20" max="33" width="4.42578125" customWidth="1"/>
+    <col min="34" max="34" width="4.42578125" style="26" customWidth="1"/>
+    <col min="35" max="39" width="4.42578125" customWidth="1"/>
+    <col min="40" max="41" width="7" customWidth="1"/>
+    <col min="42" max="42" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
@@ -1785,8 +1785,9 @@
       <c r="AM1" s="49"/>
       <c r="AN1" s="49"/>
       <c r="AO1" s="49"/>
-    </row>
-    <row r="2" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AP1" s="49"/>
+    </row>
+    <row r="2" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
@@ -1830,8 +1831,9 @@
       <c r="AM2" s="50"/>
       <c r="AN2" s="50"/>
       <c r="AO2" s="50"/>
-    </row>
-    <row r="3" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AP2" s="50"/>
+    </row>
+    <row r="3" spans="1:42" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1848,297 +1850,302 @@
         <v>274</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="G3" s="45" t="s">
+      <c r="H3" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="45"/>
-      <c r="I3" s="46" t="s">
+      <c r="I3" s="45"/>
+      <c r="J3" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="46"/>
-      <c r="K3" s="45" t="s">
+      <c r="K3" s="46"/>
+      <c r="L3" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="45"/>
-      <c r="M3" s="46" t="s">
+      <c r="M3" s="45"/>
+      <c r="N3" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="46"/>
-      <c r="O3" s="45" t="s">
+      <c r="O3" s="46"/>
+      <c r="P3" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="46" t="s">
+      <c r="Q3" s="45"/>
+      <c r="R3" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="46"/>
-      <c r="S3" s="45" t="s">
+      <c r="S3" s="46"/>
+      <c r="T3" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="T3" s="45"/>
-      <c r="U3" s="46" t="s">
+      <c r="U3" s="45"/>
+      <c r="V3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="V3" s="46"/>
-      <c r="W3" s="45" t="s">
+      <c r="W3" s="46"/>
+      <c r="X3" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="X3" s="45"/>
-      <c r="Y3" s="46" t="s">
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="Z3" s="46"/>
-      <c r="AA3" s="45" t="s">
+      <c r="AA3" s="46"/>
+      <c r="AB3" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="46" t="s">
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="46"/>
-      <c r="AE3" s="45" t="s">
+      <c r="AE3" s="46"/>
+      <c r="AF3" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="46" t="s">
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="AH3" s="46"/>
-      <c r="AI3" s="45" t="s">
+      <c r="AI3" s="46"/>
+      <c r="AJ3" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="AJ3" s="45"/>
-      <c r="AK3" s="46" t="s">
+      <c r="AK3" s="45"/>
+      <c r="AL3" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="AL3" s="46"/>
-      <c r="AM3" s="4" t="s">
+      <c r="AM3" s="46"/>
+      <c r="AN3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AN3" s="4" t="s">
+      <c r="AO3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AO3" s="4" t="s">
+      <c r="AP3" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:41" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="J4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="L4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="O4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="Q4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="R4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="S4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="T4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="U4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="V4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="V4" s="7" t="s">
+      <c r="W4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="X4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="X4" s="7" t="s">
+      <c r="Y4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="Z4" s="7" t="s">
+      <c r="AA4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AA4" s="6" t="s">
+      <c r="AB4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AB4" s="7" t="s">
+      <c r="AC4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AC4" s="6" t="s">
+      <c r="AD4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AD4" s="7" t="s">
+      <c r="AE4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AE4" s="6" t="s">
+      <c r="AF4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AF4" s="7" t="s">
+      <c r="AG4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AG4" s="22" t="s">
+      <c r="AH4" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="AH4" s="7" t="s">
+      <c r="AI4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AI4" s="6" t="s">
+      <c r="AJ4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AJ4" s="7" t="s">
+      <c r="AK4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AK4" s="6" t="s">
+      <c r="AL4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AL4" s="7" t="s">
+      <c r="AM4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AM4" s="8"/>
       <c r="AN4" s="8"/>
       <c r="AO4" s="8"/>
-    </row>
-    <row r="5" spans="1:41" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AP4" s="8"/>
+    </row>
+    <row r="5" spans="1:42" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5"/>
+      <c r="H5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="L5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="O5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="P5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="Q5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="R5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="7" t="s">
+      <c r="S5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="T5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="T5" s="7" t="s">
+      <c r="U5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="U5" s="6" t="s">
+      <c r="V5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="V5" s="7" t="s">
+      <c r="W5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="W5" s="6" t="s">
+      <c r="X5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="X5" s="7" t="s">
+      <c r="Y5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Z5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="Z5" s="7" t="s">
+      <c r="AA5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AA5" s="6" t="s">
+      <c r="AB5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AB5" s="7" t="s">
+      <c r="AC5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AC5" s="6" t="s">
+      <c r="AD5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AD5" s="7" t="s">
+      <c r="AE5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="AE5" s="6" t="s">
+      <c r="AF5" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AF5" s="7" t="s">
+      <c r="AG5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="AG5" s="22" t="s">
+      <c r="AH5" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="AH5" s="7" t="s">
+      <c r="AI5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AI5" s="6" t="s">
+      <c r="AJ5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AJ5" s="7" t="s">
+      <c r="AK5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="AK5" s="6" t="s">
+      <c r="AL5" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AL5" s="7" t="s">
+      <c r="AM5" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="AM5" s="8"/>
       <c r="AN5" s="8"/>
       <c r="AO5" s="8"/>
-    </row>
-    <row r="6" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AP5" s="8"/>
+    </row>
+    <row r="6" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>1</v>
       </c>
@@ -2152,13 +2159,11 @@
         <v>61</v>
       </c>
       <c r="E6" s="11"/>
-      <c r="F6" s="11">
+      <c r="F6" s="11"/>
+      <c r="G6" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B6&amp;" "&amp;C6,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G6" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H6" s="19" t="s">
         <v>145</v>
       </c>
@@ -2208,7 +2213,7 @@
         <v>145</v>
       </c>
       <c r="X6" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y6" s="19" t="s">
         <v>146</v>
@@ -2216,8 +2221,8 @@
       <c r="Z6" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA6" s="12" t="s">
-        <v>145</v>
+      <c r="AA6" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB6" s="12" t="s">
         <v>145</v>
@@ -2231,27 +2236,38 @@
       <c r="AE6" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF6" s="12"/>
-      <c r="AG6" s="23"/>
-      <c r="AH6" s="12"/>
-      <c r="AI6" s="12"/>
+      <c r="AF6" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG6" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH6" s="23"/>
+      <c r="AI6" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ6" s="12"/>
-      <c r="AK6" s="12"/>
+      <c r="AK6" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL6" s="12"/>
-      <c r="AM6" s="13">
-        <f t="shared" ref="AM6:AM32" si="0">COUNTIF(G6,"A")+COUNTIF(H6,"A")+COUNTIF(I6,"A")+COUNTIF(J6,"A")+COUNTIF(K6,"A")+COUNTIF(L6,"A")+COUNTIF(M6,"A")+COUNTIF(N6,"A")+COUNTIF(O6,"A")+COUNTIF(P6,"A")+COUNTIF(Q6,"A")+COUNTIF(R6,"A")+COUNTIF(S6,"A")+COUNTIF(T6,"A")+COUNTIF(U6,"A")+COUNTIF(V6,"A")+COUNTIF(W6,"A")+COUNTIF(X6,"A")+COUNTIF(Y6,"A")+COUNTIF(Z6,"A")+COUNTIF(AA6,"A")+COUNTIF(AB6,"A")+COUNTIF(AC6,"A")+COUNTIF(AD6,"A")+COUNTIF(AE6,"A")+COUNTIF(AF6,"A")+COUNTIF(AG6,"A")+COUNTIF(AH6,"A")+COUNTIF(AI6,"A")+COUNTIF(AJ6,"A")+COUNTIF(AK6,"A")+COUNTIF(AL6,"A")</f>
-        <v>22</v>
-      </c>
-      <c r="AN6" s="14">
-        <f t="shared" ref="AN6:AN32" si="1">COUNTIF(G6,"F")+COUNTIF(H6,"F")+COUNTIF(I6,"F")+COUNTIF(J6,"F")+COUNTIF(K6,"F")+COUNTIF(L6,"F")+COUNTIF(M6,"F")+COUNTIF(N6,"F")+COUNTIF(O6,"F")+COUNTIF(P6,"F")+COUNTIF(Q6,"F")+COUNTIF(R6,"F")+COUNTIF(S6,"F")+COUNTIF(T6,"F")+COUNTIF(U6,"F")+COUNTIF(V6,"F")+COUNTIF(W6,"F")+COUNTIF(X6,"F")+COUNTIF(Y6,"F")+COUNTIF(Z6,"F")+COUNTIF(AA6,"F")+COUNTIF(AB6,"F")+COUNTIF(AC6,"F")+COUNTIF(AD6,"F")+COUNTIF(AE6,"F")+COUNTIF(AF6,"F")+COUNTIF(AG6,"F")+COUNTIF(AH6,"F")+COUNTIF(AI6,"F")+COUNTIF(AJ6,"F")+COUNTIF(AK6,"F")+COUNTIF(AL6,"F")</f>
+      <c r="AM6" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN6" s="13">
+        <f t="shared" ref="AN6:AN32" si="0">COUNTIF(H6,"A")+COUNTIF(I6,"A")+COUNTIF(J6,"A")+COUNTIF(K6,"A")+COUNTIF(L6,"A")+COUNTIF(M6,"A")+COUNTIF(N6,"A")+COUNTIF(O6,"A")+COUNTIF(P6,"A")+COUNTIF(Q6,"A")+COUNTIF(R6,"A")+COUNTIF(S6,"A")+COUNTIF(T6,"A")+COUNTIF(U6,"A")+COUNTIF(V6,"A")+COUNTIF(W6,"A")+COUNTIF(X6,"A")+COUNTIF(Y6,"A")+COUNTIF(Z6,"A")+COUNTIF(AA6,"A")+COUNTIF(AB6,"A")+COUNTIF(AC6,"A")+COUNTIF(AD6,"A")+COUNTIF(AE6,"A")+COUNTIF(AF6,"A")+COUNTIF(AG6,"A")+COUNTIF(AH6,"A")+COUNTIF(AI6,"A")+COUNTIF(AJ6,"A")+COUNTIF(AK6,"A")+COUNTIF(AL6,"A")+COUNTIF(AM6,"A")</f>
+        <v>23</v>
+      </c>
+      <c r="AO6" s="14">
+        <f t="shared" ref="AO6:AO32" si="1">COUNTIF(H6,"F")+COUNTIF(I6,"F")+COUNTIF(J6,"F")+COUNTIF(K6,"F")+COUNTIF(L6,"F")+COUNTIF(M6,"F")+COUNTIF(N6,"F")+COUNTIF(O6,"F")+COUNTIF(P6,"F")+COUNTIF(Q6,"F")+COUNTIF(R6,"F")+COUNTIF(S6,"F")+COUNTIF(T6,"F")+COUNTIF(U6,"F")+COUNTIF(V6,"F")+COUNTIF(W6,"F")+COUNTIF(X6,"F")+COUNTIF(Y6,"F")+COUNTIF(Z6,"F")+COUNTIF(AA6,"F")+COUNTIF(AB6,"F")+COUNTIF(AC6,"F")+COUNTIF(AD6,"F")+COUNTIF(AE6,"F")+COUNTIF(AF6,"F")+COUNTIF(AG6,"F")+COUNTIF(AH6,"F")+COUNTIF(AI6,"F")+COUNTIF(AJ6,"F")+COUNTIF(AK6,"F")+COUNTIF(AL6,"F")+COUNTIF(AM6,"F")</f>
         <v>0</v>
       </c>
-      <c r="AO6" s="15">
-        <f t="shared" ref="AO6:AO32" si="2">IF(AM6=0,"",AM6/32)</f>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="7" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AP6" s="15">
+        <f t="shared" ref="AP6:AP32" si="2">IF(AN6=0,"",AN6/32)</f>
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>2</v>
       </c>
@@ -2265,13 +2281,11 @@
         <v>64</v>
       </c>
       <c r="E7" s="18"/>
-      <c r="F7" s="11">
+      <c r="F7" s="18"/>
+      <c r="G7" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B7&amp;" "&amp;C7,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>4.3</v>
       </c>
-      <c r="G7" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H7" s="19" t="s">
         <v>145</v>
       </c>
@@ -2321,7 +2335,7 @@
         <v>145</v>
       </c>
       <c r="X7" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y7" s="19" t="s">
         <v>146</v>
@@ -2329,13 +2343,13 @@
       <c r="Z7" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA7" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB7" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC7" s="12" t="s">
+      <c r="AA7" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB7" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC7" s="19" t="s">
         <v>145</v>
       </c>
       <c r="AD7" s="12" t="s">
@@ -2344,27 +2358,38 @@
       <c r="AE7" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF7" s="19"/>
-      <c r="AG7" s="24"/>
-      <c r="AH7" s="19"/>
-      <c r="AI7" s="19"/>
+      <c r="AF7" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG7" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH7" s="24"/>
+      <c r="AI7" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ7" s="19"/>
-      <c r="AK7" s="19"/>
+      <c r="AK7" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL7" s="19"/>
-      <c r="AM7" s="13">
+      <c r="AM7" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN7" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN7" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO7" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO7" s="15">
+      <c r="AP7" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="8" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>3</v>
       </c>
@@ -2380,13 +2405,11 @@
       <c r="E8" s="11">
         <v>1</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="11"/>
+      <c r="G8" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B8&amp;" "&amp;C8,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>3.3</v>
       </c>
-      <c r="G8" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H8" s="19" t="s">
         <v>145</v>
       </c>
@@ -2436,7 +2459,7 @@
         <v>145</v>
       </c>
       <c r="X8" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y8" s="19" t="s">
         <v>146</v>
@@ -2444,8 +2467,8 @@
       <c r="Z8" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA8" s="12" t="s">
-        <v>145</v>
+      <c r="AA8" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB8" s="12" t="s">
         <v>145</v>
@@ -2459,27 +2482,38 @@
       <c r="AE8" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="23"/>
-      <c r="AH8" s="12"/>
-      <c r="AI8" s="12"/>
+      <c r="AF8" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG8" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH8" s="23"/>
+      <c r="AI8" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ8" s="12"/>
-      <c r="AK8" s="12"/>
+      <c r="AK8" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL8" s="12"/>
-      <c r="AM8" s="13">
+      <c r="AM8" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN8" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN8" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO8" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO8" s="15">
+      <c r="AP8" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="9" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>4</v>
       </c>
@@ -2493,13 +2527,11 @@
         <v>70</v>
       </c>
       <c r="E9" s="18"/>
-      <c r="F9" s="11">
+      <c r="F9" s="18"/>
+      <c r="G9" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B9&amp;" "&amp;C9,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G9" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H9" s="19" t="s">
         <v>145</v>
       </c>
@@ -2549,7 +2581,7 @@
         <v>145</v>
       </c>
       <c r="X9" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y9" s="19" t="s">
         <v>146</v>
@@ -2557,13 +2589,13 @@
       <c r="Z9" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA9" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB9" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC9" s="12" t="s">
+      <c r="AA9" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB9" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC9" s="19" t="s">
         <v>145</v>
       </c>
       <c r="AD9" s="12" t="s">
@@ -2572,27 +2604,38 @@
       <c r="AE9" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF9" s="19"/>
-      <c r="AG9" s="24"/>
-      <c r="AH9" s="19"/>
-      <c r="AI9" s="19"/>
+      <c r="AF9" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG9" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ9" s="19"/>
-      <c r="AK9" s="19"/>
+      <c r="AK9" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL9" s="19"/>
-      <c r="AM9" s="13">
+      <c r="AM9" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN9" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN9" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO9" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO9" s="15">
+      <c r="AP9" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="10" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="10" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>5</v>
       </c>
@@ -2609,12 +2652,12 @@
         <v>1.5</v>
       </c>
       <c r="F10" s="11">
+        <v>5</v>
+      </c>
+      <c r="G10" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B10&amp;" "&amp;C10,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>4.3</v>
       </c>
-      <c r="G10" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H10" s="19" t="s">
         <v>145</v>
       </c>
@@ -2664,7 +2707,7 @@
         <v>145</v>
       </c>
       <c r="X10" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y10" s="19" t="s">
         <v>146</v>
@@ -2672,8 +2715,8 @@
       <c r="Z10" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA10" s="12" t="s">
-        <v>145</v>
+      <c r="AA10" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB10" s="12" t="s">
         <v>145</v>
@@ -2687,27 +2730,38 @@
       <c r="AE10" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF10" s="12"/>
-      <c r="AG10" s="23"/>
-      <c r="AH10" s="12"/>
-      <c r="AI10" s="12"/>
+      <c r="AF10" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG10" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH10" s="23"/>
+      <c r="AI10" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ10" s="12"/>
-      <c r="AK10" s="12"/>
+      <c r="AK10" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL10" s="12"/>
-      <c r="AM10" s="13">
+      <c r="AM10" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN10" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN10" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO10" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO10" s="15">
+      <c r="AP10" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="11" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>6</v>
       </c>
@@ -2721,13 +2775,11 @@
         <v>76</v>
       </c>
       <c r="E11" s="18"/>
-      <c r="F11" s="11">
+      <c r="F11" s="18"/>
+      <c r="G11" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B11&amp;" "&amp;C11,'Examen 1'!B$2:B$28,'Examen 1'!E$2:E$28,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G11" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H11" s="19" t="s">
         <v>145</v>
       </c>
@@ -2777,7 +2829,7 @@
         <v>145</v>
       </c>
       <c r="X11" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y11" s="19" t="s">
         <v>146</v>
@@ -2785,13 +2837,13 @@
       <c r="Z11" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA11" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB11" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC11" s="12" t="s">
+      <c r="AA11" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB11" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC11" s="19" t="s">
         <v>145</v>
       </c>
       <c r="AD11" s="12" t="s">
@@ -2800,27 +2852,38 @@
       <c r="AE11" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF11" s="19"/>
-      <c r="AG11" s="24"/>
-      <c r="AH11" s="19"/>
-      <c r="AI11" s="19"/>
+      <c r="AF11" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG11" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH11" s="24"/>
+      <c r="AI11" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ11" s="19"/>
-      <c r="AK11" s="19"/>
+      <c r="AK11" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL11" s="19"/>
-      <c r="AM11" s="13">
+      <c r="AM11" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN11" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN11" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO11" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO11" s="15">
+      <c r="AP11" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="12" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>7</v>
       </c>
@@ -2836,13 +2899,11 @@
       <c r="E12" s="11">
         <v>1</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="11"/>
+      <c r="G12" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B12&amp;" "&amp;C12,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G12" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H12" s="19" t="s">
         <v>145</v>
       </c>
@@ -2892,7 +2953,7 @@
         <v>145</v>
       </c>
       <c r="X12" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y12" s="19" t="s">
         <v>146</v>
@@ -2900,8 +2961,8 @@
       <c r="Z12" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA12" s="12" t="s">
-        <v>145</v>
+      <c r="AA12" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB12" s="12" t="s">
         <v>145</v>
@@ -2915,27 +2976,38 @@
       <c r="AE12" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF12" s="12"/>
-      <c r="AG12" s="23"/>
-      <c r="AH12" s="12"/>
-      <c r="AI12" s="12"/>
+      <c r="AF12" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG12" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH12" s="23"/>
+      <c r="AI12" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ12" s="12"/>
-      <c r="AK12" s="12"/>
+      <c r="AK12" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL12" s="12"/>
-      <c r="AM12" s="13">
+      <c r="AM12" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN12" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN12" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO12" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO12" s="15">
+      <c r="AP12" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="13" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>8</v>
       </c>
@@ -2949,13 +3021,11 @@
         <v>82</v>
       </c>
       <c r="E13" s="18"/>
-      <c r="F13" s="11">
+      <c r="F13" s="18"/>
+      <c r="G13" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B13&amp;" "&amp;C13,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="G13" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H13" s="19" t="s">
         <v>145</v>
       </c>
@@ -3005,7 +3075,7 @@
         <v>145</v>
       </c>
       <c r="X13" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y13" s="19" t="s">
         <v>146</v>
@@ -3013,13 +3083,13 @@
       <c r="Z13" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA13" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB13" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC13" s="12" t="s">
+      <c r="AA13" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB13" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC13" s="19" t="s">
         <v>145</v>
       </c>
       <c r="AD13" s="12" t="s">
@@ -3028,27 +3098,38 @@
       <c r="AE13" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF13" s="19"/>
-      <c r="AG13" s="24"/>
-      <c r="AH13" s="19"/>
-      <c r="AI13" s="19"/>
+      <c r="AF13" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG13" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH13" s="24"/>
+      <c r="AI13" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ13" s="19"/>
-      <c r="AK13" s="19"/>
+      <c r="AK13" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL13" s="19"/>
-      <c r="AM13" s="13">
+      <c r="AM13" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN13" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN13" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO13" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO13" s="15">
+      <c r="AP13" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="14" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="14" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>9</v>
       </c>
@@ -3062,13 +3143,11 @@
         <v>85</v>
       </c>
       <c r="E14" s="11"/>
-      <c r="F14" s="11">
+      <c r="F14" s="11"/>
+      <c r="G14" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B14&amp;" "&amp;C14,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G14" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H14" s="19" t="s">
         <v>145</v>
       </c>
@@ -3118,7 +3197,7 @@
         <v>145</v>
       </c>
       <c r="X14" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y14" s="19" t="s">
         <v>146</v>
@@ -3126,8 +3205,8 @@
       <c r="Z14" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA14" s="12" t="s">
-        <v>145</v>
+      <c r="AA14" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB14" s="12" t="s">
         <v>145</v>
@@ -3141,27 +3220,38 @@
       <c r="AE14" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF14" s="12"/>
-      <c r="AG14" s="23"/>
-      <c r="AH14" s="12"/>
-      <c r="AI14" s="12"/>
+      <c r="AF14" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG14" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH14" s="23"/>
+      <c r="AI14" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ14" s="12"/>
-      <c r="AK14" s="12"/>
+      <c r="AK14" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL14" s="12"/>
-      <c r="AM14" s="13">
+      <c r="AM14" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN14" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN14" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO14" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO14" s="15">
+      <c r="AP14" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="15" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>10</v>
       </c>
@@ -3177,13 +3267,11 @@
       <c r="E15" s="18">
         <v>1</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="18"/>
+      <c r="G15" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B15&amp;" "&amp;C15,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G15" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H15" s="19" t="s">
         <v>145</v>
       </c>
@@ -3233,7 +3321,7 @@
         <v>145</v>
       </c>
       <c r="X15" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y15" s="19" t="s">
         <v>146</v>
@@ -3241,13 +3329,13 @@
       <c r="Z15" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA15" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB15" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC15" s="12" t="s">
+      <c r="AA15" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB15" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC15" s="19" t="s">
         <v>145</v>
       </c>
       <c r="AD15" s="12" t="s">
@@ -3256,27 +3344,38 @@
       <c r="AE15" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF15" s="19"/>
-      <c r="AG15" s="24"/>
-      <c r="AH15" s="19"/>
-      <c r="AI15" s="19"/>
+      <c r="AF15" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG15" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH15" s="24"/>
+      <c r="AI15" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ15" s="19"/>
-      <c r="AK15" s="19"/>
+      <c r="AK15" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL15" s="19"/>
-      <c r="AM15" s="13">
+      <c r="AM15" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN15" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN15" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO15" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO15" s="15">
+      <c r="AP15" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="16" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>11</v>
       </c>
@@ -3290,13 +3389,11 @@
         <v>91</v>
       </c>
       <c r="E16" s="11"/>
-      <c r="F16" s="11">
+      <c r="F16" s="11"/>
+      <c r="G16" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B16&amp;" "&amp;C16,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>2.7</v>
       </c>
-      <c r="G16" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H16" s="19" t="s">
         <v>145</v>
       </c>
@@ -3346,7 +3443,7 @@
         <v>145</v>
       </c>
       <c r="X16" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y16" s="19" t="s">
         <v>146</v>
@@ -3354,8 +3451,8 @@
       <c r="Z16" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA16" s="12" t="s">
-        <v>145</v>
+      <c r="AA16" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB16" s="12" t="s">
         <v>145</v>
@@ -3369,27 +3466,38 @@
       <c r="AE16" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF16" s="12"/>
-      <c r="AG16" s="23"/>
-      <c r="AH16" s="12"/>
-      <c r="AI16" s="12"/>
+      <c r="AF16" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG16" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH16" s="23"/>
+      <c r="AI16" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ16" s="12"/>
-      <c r="AK16" s="12"/>
+      <c r="AK16" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL16" s="12"/>
-      <c r="AM16" s="13">
+      <c r="AM16" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN16" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN16" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO16" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO16" s="15">
+      <c r="AP16" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="17" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>12</v>
       </c>
@@ -3403,13 +3511,11 @@
         <v>94</v>
       </c>
       <c r="E17" s="18"/>
-      <c r="F17" s="11">
+      <c r="F17" s="18"/>
+      <c r="G17" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B17&amp;" "&amp;C17,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G17" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H17" s="19" t="s">
         <v>145</v>
       </c>
@@ -3459,7 +3565,7 @@
         <v>145</v>
       </c>
       <c r="X17" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y17" s="19" t="s">
         <v>146</v>
@@ -3467,13 +3573,13 @@
       <c r="Z17" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA17" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB17" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC17" s="12" t="s">
+      <c r="AA17" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB17" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC17" s="19" t="s">
         <v>145</v>
       </c>
       <c r="AD17" s="12" t="s">
@@ -3482,27 +3588,38 @@
       <c r="AE17" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF17" s="19"/>
-      <c r="AG17" s="24"/>
-      <c r="AH17" s="19"/>
-      <c r="AI17" s="19"/>
+      <c r="AF17" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG17" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH17" s="24"/>
+      <c r="AI17" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ17" s="19"/>
-      <c r="AK17" s="19"/>
+      <c r="AK17" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL17" s="19"/>
-      <c r="AM17" s="13">
+      <c r="AM17" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN17" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN17" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO17" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO17" s="15">
+      <c r="AP17" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>13</v>
       </c>
@@ -3516,13 +3633,11 @@
         <v>97</v>
       </c>
       <c r="E18" s="11"/>
-      <c r="F18" s="11">
+      <c r="F18" s="11"/>
+      <c r="G18" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B18&amp;" "&amp;C18,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>4.7</v>
       </c>
-      <c r="G18" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H18" s="19" t="s">
         <v>145</v>
       </c>
@@ -3572,7 +3687,7 @@
         <v>145</v>
       </c>
       <c r="X18" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y18" s="19" t="s">
         <v>146</v>
@@ -3580,8 +3695,8 @@
       <c r="Z18" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA18" s="12" t="s">
-        <v>145</v>
+      <c r="AA18" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB18" s="12" t="s">
         <v>145</v>
@@ -3595,27 +3710,38 @@
       <c r="AE18" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF18" s="12"/>
-      <c r="AG18" s="23"/>
-      <c r="AH18" s="12"/>
-      <c r="AI18" s="12"/>
+      <c r="AF18" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG18" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH18" s="23"/>
+      <c r="AI18" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ18" s="12"/>
-      <c r="AK18" s="12"/>
+      <c r="AK18" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL18" s="12"/>
-      <c r="AM18" s="13">
+      <c r="AM18" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN18" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN18" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO18" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO18" s="15">
+      <c r="AP18" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="19" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>14</v>
       </c>
@@ -3631,13 +3757,11 @@
       <c r="E19" s="18">
         <v>1</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="18"/>
+      <c r="G19" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B19&amp;" "&amp;C19,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>4.9000000000000004</v>
       </c>
-      <c r="G19" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H19" s="19" t="s">
         <v>145</v>
       </c>
@@ -3687,7 +3811,7 @@
         <v>145</v>
       </c>
       <c r="X19" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y19" s="19" t="s">
         <v>146</v>
@@ -3695,13 +3819,13 @@
       <c r="Z19" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA19" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB19" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC19" s="12" t="s">
+      <c r="AA19" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB19" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC19" s="19" t="s">
         <v>145</v>
       </c>
       <c r="AD19" s="12" t="s">
@@ -3710,27 +3834,38 @@
       <c r="AE19" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF19" s="19"/>
-      <c r="AG19" s="24"/>
-      <c r="AH19" s="19"/>
-      <c r="AI19" s="19"/>
+      <c r="AF19" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG19" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH19" s="24"/>
+      <c r="AI19" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ19" s="19"/>
-      <c r="AK19" s="19"/>
+      <c r="AK19" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL19" s="19"/>
-      <c r="AM19" s="13">
+      <c r="AM19" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN19" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN19" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO19" s="15">
+      <c r="AP19" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>15</v>
       </c>
@@ -3744,13 +3879,11 @@
         <v>103</v>
       </c>
       <c r="E20" s="11"/>
-      <c r="F20" s="11">
+      <c r="F20" s="11"/>
+      <c r="G20" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B20&amp;" "&amp;C20,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>4.8</v>
       </c>
-      <c r="G20" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H20" s="19" t="s">
         <v>145</v>
       </c>
@@ -3800,7 +3933,7 @@
         <v>145</v>
       </c>
       <c r="X20" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y20" s="19" t="s">
         <v>146</v>
@@ -3808,8 +3941,8 @@
       <c r="Z20" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA20" s="12" t="s">
-        <v>145</v>
+      <c r="AA20" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB20" s="12" t="s">
         <v>145</v>
@@ -3823,27 +3956,38 @@
       <c r="AE20" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF20" s="12"/>
-      <c r="AG20" s="23"/>
-      <c r="AH20" s="12"/>
-      <c r="AI20" s="12"/>
+      <c r="AF20" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG20" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH20" s="23"/>
+      <c r="AI20" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ20" s="12"/>
-      <c r="AK20" s="12"/>
+      <c r="AK20" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL20" s="12"/>
-      <c r="AM20" s="13">
+      <c r="AM20" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN20" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN20" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO20" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO20" s="15">
+      <c r="AP20" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="28">
         <v>16</v>
       </c>
@@ -3857,13 +4001,11 @@
         <v>106</v>
       </c>
       <c r="E21" s="30"/>
-      <c r="F21" s="30">
+      <c r="F21" s="30"/>
+      <c r="G21" s="30">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B21&amp;" "&amp;C21,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G21" s="31" t="s">
-        <v>145</v>
-      </c>
       <c r="H21" s="31" t="s">
         <v>145</v>
       </c>
@@ -3913,7 +4055,7 @@
         <v>145</v>
       </c>
       <c r="X21" s="31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y21" s="31" t="s">
         <v>146</v>
@@ -3922,7 +4064,7 @@
         <v>146</v>
       </c>
       <c r="AA21" s="31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AB21" s="31" t="s">
         <v>145</v>
@@ -3933,30 +4075,41 @@
       <c r="AD21" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="AE21" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AF21" s="31"/>
-      <c r="AG21" s="33"/>
-      <c r="AH21" s="31"/>
-      <c r="AI21" s="31"/>
+      <c r="AE21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF21" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG21" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH21" s="33"/>
+      <c r="AI21" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ21" s="31"/>
-      <c r="AK21" s="31"/>
+      <c r="AK21" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL21" s="31"/>
-      <c r="AM21" s="28">
+      <c r="AM21" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN21" s="28">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN21" s="28">
+        <v>23</v>
+      </c>
+      <c r="AO21" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO21" s="32">
+      <c r="AP21" s="32">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="22" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>17</v>
       </c>
@@ -3970,13 +4123,11 @@
         <v>109</v>
       </c>
       <c r="E22" s="11"/>
-      <c r="F22" s="11">
+      <c r="F22" s="11"/>
+      <c r="G22" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B22&amp;" "&amp;C22,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>4.8</v>
       </c>
-      <c r="G22" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H22" s="19" t="s">
         <v>145</v>
       </c>
@@ -4026,7 +4177,7 @@
         <v>145</v>
       </c>
       <c r="X22" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y22" s="19" t="s">
         <v>146</v>
@@ -4034,8 +4185,8 @@
       <c r="Z22" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA22" s="12" t="s">
-        <v>145</v>
+      <c r="AA22" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB22" s="12" t="s">
         <v>145</v>
@@ -4049,27 +4200,38 @@
       <c r="AE22" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF22" s="12"/>
-      <c r="AG22" s="23"/>
-      <c r="AH22" s="12"/>
-      <c r="AI22" s="12"/>
+      <c r="AF22" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG22" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH22" s="23"/>
+      <c r="AI22" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ22" s="12"/>
-      <c r="AK22" s="12"/>
+      <c r="AK22" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL22" s="12"/>
-      <c r="AM22" s="13">
+      <c r="AM22" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN22" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN22" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO22" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO22" s="15">
+      <c r="AP22" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="23" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="23" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>18</v>
       </c>
@@ -4083,13 +4245,11 @@
         <v>112</v>
       </c>
       <c r="E23" s="18"/>
-      <c r="F23" s="11">
+      <c r="F23" s="18"/>
+      <c r="G23" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B23&amp;" "&amp;C23,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G23" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H23" s="19" t="s">
         <v>145</v>
       </c>
@@ -4139,7 +4299,7 @@
         <v>145</v>
       </c>
       <c r="X23" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y23" s="19" t="s">
         <v>146</v>
@@ -4147,13 +4307,13 @@
       <c r="Z23" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA23" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB23" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC23" s="12" t="s">
+      <c r="AA23" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB23" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC23" s="19" t="s">
         <v>145</v>
       </c>
       <c r="AD23" s="12" t="s">
@@ -4162,27 +4322,38 @@
       <c r="AE23" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF23" s="19"/>
-      <c r="AG23" s="24"/>
-      <c r="AH23" s="19"/>
-      <c r="AI23" s="19"/>
+      <c r="AF23" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG23" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH23" s="24"/>
+      <c r="AI23" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ23" s="19"/>
-      <c r="AK23" s="19"/>
+      <c r="AK23" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL23" s="19"/>
-      <c r="AM23" s="13">
+      <c r="AM23" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN23" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN23" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO23" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO23" s="15">
+      <c r="AP23" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="24" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>19</v>
       </c>
@@ -4196,13 +4367,11 @@
         <v>115</v>
       </c>
       <c r="E24" s="11"/>
-      <c r="F24" s="11">
+      <c r="F24" s="11"/>
+      <c r="G24" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B24&amp;" "&amp;C24,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G24" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H24" s="19" t="s">
         <v>145</v>
       </c>
@@ -4252,7 +4421,7 @@
         <v>145</v>
       </c>
       <c r="X24" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y24" s="19" t="s">
         <v>146</v>
@@ -4260,8 +4429,8 @@
       <c r="Z24" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA24" s="12" t="s">
-        <v>145</v>
+      <c r="AA24" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB24" s="12" t="s">
         <v>145</v>
@@ -4275,27 +4444,38 @@
       <c r="AE24" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF24" s="12"/>
-      <c r="AG24" s="23"/>
-      <c r="AH24" s="12"/>
-      <c r="AI24" s="12"/>
+      <c r="AF24" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG24" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH24" s="23"/>
+      <c r="AI24" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ24" s="12"/>
-      <c r="AK24" s="12"/>
+      <c r="AK24" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL24" s="12"/>
-      <c r="AM24" s="13">
+      <c r="AM24" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN24" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN24" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO24" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO24" s="15">
+      <c r="AP24" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="25" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="25" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>20</v>
       </c>
@@ -4309,13 +4489,11 @@
         <v>118</v>
       </c>
       <c r="E25" s="18"/>
-      <c r="F25" s="11">
+      <c r="F25" s="18"/>
+      <c r="G25" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B25&amp;" "&amp;C25,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G25" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H25" s="19" t="s">
         <v>145</v>
       </c>
@@ -4365,7 +4543,7 @@
         <v>145</v>
       </c>
       <c r="X25" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y25" s="19" t="s">
         <v>146</v>
@@ -4373,13 +4551,13 @@
       <c r="Z25" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA25" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB25" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC25" s="12" t="s">
+      <c r="AA25" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB25" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC25" s="19" t="s">
         <v>145</v>
       </c>
       <c r="AD25" s="12" t="s">
@@ -4388,27 +4566,38 @@
       <c r="AE25" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF25" s="19"/>
-      <c r="AG25" s="24"/>
-      <c r="AH25" s="19"/>
-      <c r="AI25" s="19"/>
+      <c r="AF25" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG25" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH25" s="24"/>
+      <c r="AI25" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ25" s="19"/>
-      <c r="AK25" s="19"/>
+      <c r="AK25" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL25" s="19"/>
-      <c r="AM25" s="13">
+      <c r="AM25" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN25" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN25" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO25" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO25" s="15">
+      <c r="AP25" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="26" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>21</v>
       </c>
@@ -4422,13 +4611,11 @@
         <v>121</v>
       </c>
       <c r="E26" s="11"/>
-      <c r="F26" s="11">
+      <c r="F26" s="11"/>
+      <c r="G26" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B26&amp;" "&amp;C26,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G26" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H26" s="19" t="s">
         <v>145</v>
       </c>
@@ -4478,7 +4665,7 @@
         <v>145</v>
       </c>
       <c r="X26" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y26" s="19" t="s">
         <v>146</v>
@@ -4486,8 +4673,8 @@
       <c r="Z26" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA26" s="12" t="s">
-        <v>145</v>
+      <c r="AA26" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB26" s="12" t="s">
         <v>145</v>
@@ -4501,27 +4688,38 @@
       <c r="AE26" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF26" s="12"/>
-      <c r="AG26" s="23"/>
-      <c r="AH26" s="12"/>
-      <c r="AI26" s="12"/>
+      <c r="AF26" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG26" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH26" s="23"/>
+      <c r="AI26" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ26" s="12"/>
-      <c r="AK26" s="12"/>
+      <c r="AK26" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL26" s="12"/>
-      <c r="AM26" s="13">
+      <c r="AM26" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN26" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN26" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO26" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO26" s="15">
+      <c r="AP26" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="27" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>22</v>
       </c>
@@ -4537,13 +4735,11 @@
       <c r="E27" s="18">
         <v>2</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="18"/>
+      <c r="G27" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B27&amp;" "&amp;C27,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>3.1</v>
       </c>
-      <c r="G27" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H27" s="19" t="s">
         <v>145</v>
       </c>
@@ -4593,7 +4789,7 @@
         <v>145</v>
       </c>
       <c r="X27" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y27" s="19" t="s">
         <v>146</v>
@@ -4601,13 +4797,13 @@
       <c r="Z27" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA27" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB27" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC27" s="12" t="s">
+      <c r="AA27" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB27" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC27" s="19" t="s">
         <v>145</v>
       </c>
       <c r="AD27" s="12" t="s">
@@ -4616,27 +4812,38 @@
       <c r="AE27" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF27" s="19"/>
-      <c r="AG27" s="24"/>
-      <c r="AH27" s="19"/>
-      <c r="AI27" s="19"/>
+      <c r="AF27" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG27" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH27" s="24"/>
+      <c r="AI27" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ27" s="19"/>
-      <c r="AK27" s="19"/>
+      <c r="AK27" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL27" s="19"/>
-      <c r="AM27" s="13">
+      <c r="AM27" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN27" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN27" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO27" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO27" s="15">
+      <c r="AP27" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="28" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>23</v>
       </c>
@@ -4650,13 +4857,11 @@
         <v>127</v>
       </c>
       <c r="E28" s="11"/>
-      <c r="F28" s="11">
+      <c r="F28" s="11"/>
+      <c r="G28" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B28&amp;" "&amp;C28,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G28" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H28" s="19" t="s">
         <v>145</v>
       </c>
@@ -4706,7 +4911,7 @@
         <v>145</v>
       </c>
       <c r="X28" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y28" s="19" t="s">
         <v>146</v>
@@ -4714,8 +4919,8 @@
       <c r="Z28" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA28" s="12" t="s">
-        <v>145</v>
+      <c r="AA28" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB28" s="12" t="s">
         <v>145</v>
@@ -4729,27 +4934,38 @@
       <c r="AE28" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF28" s="12"/>
-      <c r="AG28" s="23"/>
-      <c r="AH28" s="12"/>
-      <c r="AI28" s="12"/>
+      <c r="AF28" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG28" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH28" s="23"/>
+      <c r="AI28" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ28" s="12"/>
-      <c r="AK28" s="12"/>
+      <c r="AK28" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL28" s="12"/>
-      <c r="AM28" s="13">
+      <c r="AM28" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN28" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN28" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO28" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO28" s="15">
+      <c r="AP28" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="29" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>24</v>
       </c>
@@ -4765,13 +4981,11 @@
       <c r="E29" s="18">
         <v>1.5</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="18"/>
+      <c r="G29" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B29&amp;" "&amp;C29,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>3.2</v>
       </c>
-      <c r="G29" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H29" s="19" t="s">
         <v>145</v>
       </c>
@@ -4821,7 +5035,7 @@
         <v>145</v>
       </c>
       <c r="X29" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y29" s="19" t="s">
         <v>146</v>
@@ -4829,13 +5043,13 @@
       <c r="Z29" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA29" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB29" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC29" s="12" t="s">
+      <c r="AA29" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB29" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC29" s="19" t="s">
         <v>145</v>
       </c>
       <c r="AD29" s="12" t="s">
@@ -4844,27 +5058,38 @@
       <c r="AE29" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF29" s="19"/>
-      <c r="AG29" s="24"/>
-      <c r="AH29" s="19"/>
-      <c r="AI29" s="19"/>
+      <c r="AF29" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG29" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH29" s="24"/>
+      <c r="AI29" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ29" s="19"/>
-      <c r="AK29" s="19"/>
+      <c r="AK29" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL29" s="19"/>
-      <c r="AM29" s="13">
+      <c r="AM29" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN29" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN29" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO29" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO29" s="15">
+      <c r="AP29" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="30" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>25</v>
       </c>
@@ -4880,13 +5105,11 @@
       <c r="E30" s="11">
         <v>1</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="11"/>
+      <c r="G30" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B30&amp;" "&amp;C30,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>4.5</v>
       </c>
-      <c r="G30" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H30" s="19" t="s">
         <v>145</v>
       </c>
@@ -4936,7 +5159,7 @@
         <v>145</v>
       </c>
       <c r="X30" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y30" s="19" t="s">
         <v>146</v>
@@ -4944,8 +5167,8 @@
       <c r="Z30" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA30" s="12" t="s">
-        <v>145</v>
+      <c r="AA30" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB30" s="12" t="s">
         <v>145</v>
@@ -4959,27 +5182,38 @@
       <c r="AE30" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF30" s="12"/>
-      <c r="AG30" s="23"/>
-      <c r="AH30" s="12"/>
-      <c r="AI30" s="12"/>
+      <c r="AF30" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG30" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH30" s="23"/>
+      <c r="AI30" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ30" s="12"/>
-      <c r="AK30" s="12"/>
+      <c r="AK30" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL30" s="12"/>
-      <c r="AM30" s="13">
+      <c r="AM30" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN30" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN30" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO30" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO30" s="15">
+      <c r="AP30" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="31" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>26</v>
       </c>
@@ -4995,13 +5229,13 @@
       <c r="E31" s="18">
         <v>2</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="18">
+        <v>5</v>
+      </c>
+      <c r="G31" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B31&amp;" "&amp;C31,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>3.9</v>
       </c>
-      <c r="G31" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H31" s="19" t="s">
         <v>145</v>
       </c>
@@ -5051,7 +5285,7 @@
         <v>145</v>
       </c>
       <c r="X31" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y31" s="19" t="s">
         <v>146</v>
@@ -5059,13 +5293,13 @@
       <c r="Z31" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA31" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB31" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC31" s="12" t="s">
+      <c r="AA31" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB31" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC31" s="19" t="s">
         <v>145</v>
       </c>
       <c r="AD31" s="12" t="s">
@@ -5074,27 +5308,38 @@
       <c r="AE31" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF31" s="19"/>
-      <c r="AG31" s="24"/>
-      <c r="AH31" s="19"/>
-      <c r="AI31" s="19"/>
+      <c r="AF31" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG31" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH31" s="24"/>
+      <c r="AI31" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ31" s="19"/>
-      <c r="AK31" s="19"/>
+      <c r="AK31" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL31" s="19"/>
-      <c r="AM31" s="13">
+      <c r="AM31" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN31" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN31" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO31" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO31" s="15">
+      <c r="AP31" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="32" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>27</v>
       </c>
@@ -5110,13 +5355,11 @@
       <c r="E32" s="11">
         <v>1</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="11"/>
+      <c r="G32" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B32&amp;" "&amp;C32,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G32" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H32" s="19" t="s">
         <v>145</v>
       </c>
@@ -5166,7 +5409,7 @@
         <v>145</v>
       </c>
       <c r="X32" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y32" s="19" t="s">
         <v>146</v>
@@ -5174,8 +5417,8 @@
       <c r="Z32" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AA32" s="12" t="s">
-        <v>145</v>
+      <c r="AA32" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AB32" s="12" t="s">
         <v>145</v>
@@ -5189,27 +5432,38 @@
       <c r="AE32" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF32" s="12"/>
-      <c r="AG32" s="23"/>
-      <c r="AH32" s="12"/>
-      <c r="AI32" s="12"/>
+      <c r="AF32" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG32" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH32" s="23"/>
+      <c r="AI32" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AJ32" s="12"/>
-      <c r="AK32" s="12"/>
+      <c r="AK32" s="19" t="s">
+        <v>146</v>
+      </c>
       <c r="AL32" s="12"/>
-      <c r="AM32" s="13">
+      <c r="AM32" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN32" s="13">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AN32" s="14">
+        <v>23</v>
+      </c>
+      <c r="AO32" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO32" s="15">
+      <c r="AP32" s="15">
         <f t="shared" si="2"/>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="33" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="47" t="s">
         <v>140</v>
       </c>
@@ -5218,12 +5472,9 @@
       <c r="D33" s="47"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
-      <c r="G33" s="20">
-        <f t="shared" ref="G33:AL33" si="3">COUNTIF(G6:G32,"A")</f>
-        <v>27</v>
-      </c>
+      <c r="G33" s="1"/>
       <c r="H33" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H33:AM33" si="3">COUNTIF(H6:H32,"A")</f>
         <v>27</v>
       </c>
       <c r="I33" s="20">
@@ -5288,7 +5539,7 @@
       </c>
       <c r="X33" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Y33" s="20">
         <f t="shared" si="3"/>
@@ -5300,7 +5551,7 @@
       </c>
       <c r="AA33" s="20">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AB33" s="20">
         <f t="shared" si="3"/>
@@ -5320,13 +5571,13 @@
       </c>
       <c r="AF33" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG33" s="25">
+        <v>27</v>
+      </c>
+      <c r="AG33" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH33" s="20">
+        <v>27</v>
+      </c>
+      <c r="AH33" s="25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5346,11 +5597,15 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AM33" s="5"/>
+      <c r="AM33" s="20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN33" s="5"/>
       <c r="AO33" s="5"/>
-    </row>
-    <row r="34" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AP33" s="5"/>
+    </row>
+    <row r="34" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="48" t="s">
         <v>141</v>
       </c>
@@ -5394,41 +5649,42 @@
       <c r="AM34" s="48"/>
       <c r="AN34" s="48"/>
       <c r="AO34" s="48"/>
-    </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="AG35" s="26" t="s">
+      <c r="AP34" s="48"/>
+    </row>
+    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="AH35" s="26" t="s">
         <v>147</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="AL3:AM3"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A34:AO34"/>
-    <mergeCell ref="A1:AO1"/>
-    <mergeCell ref="A2:AO2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="A34:AP34"/>
+    <mergeCell ref="A1:AP1"/>
+    <mergeCell ref="A2:AP2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AJ3:AK3"/>
   </mergeCells>
-  <conditionalFormatting sqref="AO6:AO32">
+  <conditionalFormatting sqref="AP6:AP32">
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AO6&lt;0.8</formula>
+      <formula>AP6&lt;0.8</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>AO6&gt;=0.8</formula>
+      <formula>AP6&gt;=0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5502,19 +5758,19 @@
         <v>61</v>
       </c>
       <c r="E3" s="13">
-        <f>Asistencia!AM6</f>
-        <v>22</v>
+        <f>Asistencia!AN6</f>
+        <v>23</v>
       </c>
       <c r="F3" s="14">
-        <f>Asistencia!AN6</f>
+        <f>Asistencia!AO6</f>
         <v>0</v>
       </c>
       <c r="G3" s="15">
-        <f>Asistencia!AO6</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP6</f>
+        <v>0.71875</v>
       </c>
       <c r="H3" s="9" t="str">
-        <f>IF(Asistencia!AO6="","Sin datos",IF(Asistencia!AO6&gt;=0.8,"✅ Asistencia!AB6ARegular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP6="","Sin datos",IF(Asistencia!AP6&gt;=0.8,"✅ Asistencia!AB6ARegular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5532,19 +5788,19 @@
         <v>64</v>
       </c>
       <c r="E4" s="13">
-        <f>Asistencia!AM7</f>
-        <v>22</v>
+        <f>Asistencia!AN7</f>
+        <v>23</v>
       </c>
       <c r="F4" s="14">
-        <f>Asistencia!AN7</f>
+        <f>Asistencia!AO7</f>
         <v>0</v>
       </c>
       <c r="G4" s="15">
-        <f>Asistencia!AO7</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP7</f>
+        <v>0.71875</v>
       </c>
       <c r="H4" s="16" t="str">
-        <f>IF(Asistencia!AO7="","Sin datos",IF(Asistencia!AO7&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP7="","Sin datos",IF(Asistencia!AP7&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5562,19 +5818,19 @@
         <v>67</v>
       </c>
       <c r="E5" s="13">
-        <f>Asistencia!AM8</f>
-        <v>22</v>
+        <f>Asistencia!AN8</f>
+        <v>23</v>
       </c>
       <c r="F5" s="14">
-        <f>Asistencia!AN8</f>
+        <f>Asistencia!AO8</f>
         <v>0</v>
       </c>
       <c r="G5" s="15">
-        <f>Asistencia!AO8</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP8</f>
+        <v>0.71875</v>
       </c>
       <c r="H5" s="9" t="str">
-        <f>IF(Asistencia!AO8="","Sin datos",IF(Asistencia!AO8&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP8="","Sin datos",IF(Asistencia!AP8&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5592,19 +5848,19 @@
         <v>70</v>
       </c>
       <c r="E6" s="13">
-        <f>Asistencia!AM9</f>
-        <v>22</v>
+        <f>Asistencia!AN9</f>
+        <v>23</v>
       </c>
       <c r="F6" s="14">
-        <f>Asistencia!AN9</f>
+        <f>Asistencia!AO9</f>
         <v>0</v>
       </c>
       <c r="G6" s="15">
-        <f>Asistencia!AO9</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP9</f>
+        <v>0.71875</v>
       </c>
       <c r="H6" s="16" t="str">
-        <f>IF(Asistencia!AO9="","Sin datos",IF(Asistencia!AO9&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP9="","Sin datos",IF(Asistencia!AP9&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5622,19 +5878,19 @@
         <v>73</v>
       </c>
       <c r="E7" s="13">
-        <f>Asistencia!AM10</f>
-        <v>22</v>
+        <f>Asistencia!AN10</f>
+        <v>23</v>
       </c>
       <c r="F7" s="14">
-        <f>Asistencia!AN10</f>
+        <f>Asistencia!AO10</f>
         <v>0</v>
       </c>
       <c r="G7" s="15">
-        <f>Asistencia!AO10</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP10</f>
+        <v>0.71875</v>
       </c>
       <c r="H7" s="9" t="str">
-        <f>IF(Asistencia!AO10="","Sin datos",IF(Asistencia!AO10&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP10="","Sin datos",IF(Asistencia!AP10&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5652,19 +5908,19 @@
         <v>76</v>
       </c>
       <c r="E8" s="13">
-        <f>Asistencia!AM11</f>
-        <v>22</v>
+        <f>Asistencia!AN11</f>
+        <v>23</v>
       </c>
       <c r="F8" s="14">
-        <f>Asistencia!AN11</f>
+        <f>Asistencia!AO11</f>
         <v>0</v>
       </c>
       <c r="G8" s="15">
-        <f>Asistencia!AO11</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP11</f>
+        <v>0.71875</v>
       </c>
       <c r="H8" s="16" t="str">
-        <f>IF(Asistencia!AO11="","Sin datos",IF(Asistencia!AO11&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP11="","Sin datos",IF(Asistencia!AP11&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5682,19 +5938,19 @@
         <v>79</v>
       </c>
       <c r="E9" s="13">
-        <f>Asistencia!AM12</f>
-        <v>22</v>
+        <f>Asistencia!AN12</f>
+        <v>23</v>
       </c>
       <c r="F9" s="14">
-        <f>Asistencia!AN12</f>
+        <f>Asistencia!AO12</f>
         <v>0</v>
       </c>
       <c r="G9" s="15">
-        <f>Asistencia!AO12</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP12</f>
+        <v>0.71875</v>
       </c>
       <c r="H9" s="9" t="str">
-        <f>IF(Asistencia!AO12="","Sin datos",IF(Asistencia!AO12&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP12="","Sin datos",IF(Asistencia!AP12&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5712,19 +5968,19 @@
         <v>82</v>
       </c>
       <c r="E10" s="13">
-        <f>Asistencia!AM13</f>
-        <v>22</v>
+        <f>Asistencia!AN13</f>
+        <v>23</v>
       </c>
       <c r="F10" s="14">
-        <f>Asistencia!AN13</f>
+        <f>Asistencia!AO13</f>
         <v>0</v>
       </c>
       <c r="G10" s="15">
-        <f>Asistencia!AO13</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP13</f>
+        <v>0.71875</v>
       </c>
       <c r="H10" s="16" t="str">
-        <f>IF(Asistencia!AO13="","Sin datos",IF(Asistencia!AO13&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP13="","Sin datos",IF(Asistencia!AP13&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5742,19 +5998,19 @@
         <v>85</v>
       </c>
       <c r="E11" s="13">
-        <f>Asistencia!AM14</f>
-        <v>22</v>
+        <f>Asistencia!AN14</f>
+        <v>23</v>
       </c>
       <c r="F11" s="14">
-        <f>Asistencia!AN14</f>
+        <f>Asistencia!AO14</f>
         <v>0</v>
       </c>
       <c r="G11" s="15">
-        <f>Asistencia!AO14</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP14</f>
+        <v>0.71875</v>
       </c>
       <c r="H11" s="9" t="str">
-        <f>IF(Asistencia!AO14="","Sin datos",IF(Asistencia!AO14&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP14="","Sin datos",IF(Asistencia!AP14&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5772,19 +6028,19 @@
         <v>88</v>
       </c>
       <c r="E12" s="13">
-        <f>Asistencia!AM15</f>
-        <v>22</v>
+        <f>Asistencia!AN15</f>
+        <v>23</v>
       </c>
       <c r="F12" s="14">
-        <f>Asistencia!AN15</f>
+        <f>Asistencia!AO15</f>
         <v>0</v>
       </c>
       <c r="G12" s="15">
-        <f>Asistencia!AO15</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP15</f>
+        <v>0.71875</v>
       </c>
       <c r="H12" s="16" t="str">
-        <f>IF(Asistencia!AO15="","Sin datos",IF(Asistencia!AO15&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP15="","Sin datos",IF(Asistencia!AP15&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5802,19 +6058,19 @@
         <v>91</v>
       </c>
       <c r="E13" s="13">
-        <f>Asistencia!AM16</f>
-        <v>22</v>
+        <f>Asistencia!AN16</f>
+        <v>23</v>
       </c>
       <c r="F13" s="14">
-        <f>Asistencia!AN16</f>
+        <f>Asistencia!AO16</f>
         <v>0</v>
       </c>
       <c r="G13" s="15">
-        <f>Asistencia!AO16</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP16</f>
+        <v>0.71875</v>
       </c>
       <c r="H13" s="9" t="str">
-        <f>IF(Asistencia!AO16="","Sin datos",IF(Asistencia!AO16&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP16="","Sin datos",IF(Asistencia!AP16&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5832,19 +6088,19 @@
         <v>94</v>
       </c>
       <c r="E14" s="13">
-        <f>Asistencia!AM17</f>
-        <v>22</v>
+        <f>Asistencia!AN17</f>
+        <v>23</v>
       </c>
       <c r="F14" s="14">
-        <f>Asistencia!AN17</f>
+        <f>Asistencia!AO17</f>
         <v>0</v>
       </c>
       <c r="G14" s="15">
-        <f>Asistencia!AO17</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP17</f>
+        <v>0.71875</v>
       </c>
       <c r="H14" s="16" t="str">
-        <f>IF(Asistencia!AO17="","Sin datos",IF(Asistencia!AO17&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP17="","Sin datos",IF(Asistencia!AP17&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5862,19 +6118,19 @@
         <v>97</v>
       </c>
       <c r="E15" s="13">
-        <f>Asistencia!AM18</f>
-        <v>22</v>
+        <f>Asistencia!AN18</f>
+        <v>23</v>
       </c>
       <c r="F15" s="14">
-        <f>Asistencia!AN18</f>
+        <f>Asistencia!AO18</f>
         <v>0</v>
       </c>
       <c r="G15" s="15">
-        <f>Asistencia!AO18</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP18</f>
+        <v>0.71875</v>
       </c>
       <c r="H15" s="9" t="str">
-        <f>IF(Asistencia!AO18="","Sin datos",IF(Asistencia!AO18&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP18="","Sin datos",IF(Asistencia!AP18&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5892,19 +6148,19 @@
         <v>100</v>
       </c>
       <c r="E16" s="13">
-        <f>Asistencia!AM19</f>
-        <v>22</v>
+        <f>Asistencia!AN19</f>
+        <v>23</v>
       </c>
       <c r="F16" s="14">
-        <f>Asistencia!AN19</f>
+        <f>Asistencia!AO19</f>
         <v>0</v>
       </c>
       <c r="G16" s="15">
-        <f>Asistencia!AO19</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP19</f>
+        <v>0.71875</v>
       </c>
       <c r="H16" s="16" t="str">
-        <f>IF(Asistencia!AO19="","Sin datos",IF(Asistencia!AO19&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP19="","Sin datos",IF(Asistencia!AP19&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5922,19 +6178,19 @@
         <v>103</v>
       </c>
       <c r="E17" s="13">
-        <f>Asistencia!AM20</f>
-        <v>22</v>
+        <f>Asistencia!AN20</f>
+        <v>23</v>
       </c>
       <c r="F17" s="14">
-        <f>Asistencia!AN20</f>
+        <f>Asistencia!AO20</f>
         <v>0</v>
       </c>
       <c r="G17" s="15">
-        <f>Asistencia!AO20</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP20</f>
+        <v>0.71875</v>
       </c>
       <c r="H17" s="9" t="str">
-        <f>IF(Asistencia!AO20="","Sin datos",IF(Asistencia!AO20&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP20="","Sin datos",IF(Asistencia!AP20&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5952,19 +6208,19 @@
         <v>106</v>
       </c>
       <c r="E18" s="13">
-        <f>Asistencia!AM21</f>
-        <v>22</v>
+        <f>Asistencia!AN21</f>
+        <v>23</v>
       </c>
       <c r="F18" s="14">
-        <f>Asistencia!AN21</f>
+        <f>Asistencia!AO21</f>
         <v>0</v>
       </c>
       <c r="G18" s="15">
-        <f>Asistencia!AO21</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP21</f>
+        <v>0.71875</v>
       </c>
       <c r="H18" s="16" t="str">
-        <f>IF(Asistencia!AO21="","Sin datos",IF(Asistencia!AO21&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP21="","Sin datos",IF(Asistencia!AP21&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5982,19 +6238,19 @@
         <v>109</v>
       </c>
       <c r="E19" s="13">
-        <f>Asistencia!AM22</f>
-        <v>22</v>
+        <f>Asistencia!AN22</f>
+        <v>23</v>
       </c>
       <c r="F19" s="14">
-        <f>Asistencia!AN22</f>
+        <f>Asistencia!AO22</f>
         <v>0</v>
       </c>
       <c r="G19" s="15">
-        <f>Asistencia!AO22</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP22</f>
+        <v>0.71875</v>
       </c>
       <c r="H19" s="9" t="str">
-        <f>IF(Asistencia!AO22="","Sin datos",IF(Asistencia!AO22&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP22="","Sin datos",IF(Asistencia!AP22&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -6012,19 +6268,19 @@
         <v>112</v>
       </c>
       <c r="E20" s="13">
-        <f>Asistencia!AM23</f>
-        <v>22</v>
+        <f>Asistencia!AN23</f>
+        <v>23</v>
       </c>
       <c r="F20" s="14">
-        <f>Asistencia!AN23</f>
+        <f>Asistencia!AO23</f>
         <v>0</v>
       </c>
       <c r="G20" s="15">
-        <f>Asistencia!AO23</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP23</f>
+        <v>0.71875</v>
       </c>
       <c r="H20" s="16" t="str">
-        <f>IF(Asistencia!AO23="","Sin datos",IF(Asistencia!AO23&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP23="","Sin datos",IF(Asistencia!AP23&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -6042,19 +6298,19 @@
         <v>115</v>
       </c>
       <c r="E21" s="13">
-        <f>Asistencia!AM24</f>
-        <v>22</v>
+        <f>Asistencia!AN24</f>
+        <v>23</v>
       </c>
       <c r="F21" s="14">
-        <f>Asistencia!AN24</f>
+        <f>Asistencia!AO24</f>
         <v>0</v>
       </c>
       <c r="G21" s="15">
-        <f>Asistencia!AO24</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP24</f>
+        <v>0.71875</v>
       </c>
       <c r="H21" s="9" t="str">
-        <f>IF(Asistencia!AO24="","Sin datos",IF(Asistencia!AO24&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP24="","Sin datos",IF(Asistencia!AP24&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -6072,19 +6328,19 @@
         <v>118</v>
       </c>
       <c r="E22" s="13">
-        <f>Asistencia!AM25</f>
-        <v>22</v>
+        <f>Asistencia!AN25</f>
+        <v>23</v>
       </c>
       <c r="F22" s="14">
-        <f>Asistencia!AN25</f>
+        <f>Asistencia!AO25</f>
         <v>0</v>
       </c>
       <c r="G22" s="15">
-        <f>Asistencia!AO25</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP25</f>
+        <v>0.71875</v>
       </c>
       <c r="H22" s="16" t="str">
-        <f>IF(Asistencia!AO25="","Sin datos",IF(Asistencia!AO25&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP25="","Sin datos",IF(Asistencia!AP25&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -6102,19 +6358,19 @@
         <v>121</v>
       </c>
       <c r="E23" s="13">
-        <f>Asistencia!AM26</f>
-        <v>22</v>
+        <f>Asistencia!AN26</f>
+        <v>23</v>
       </c>
       <c r="F23" s="14">
-        <f>Asistencia!AN26</f>
+        <f>Asistencia!AO26</f>
         <v>0</v>
       </c>
       <c r="G23" s="15">
-        <f>Asistencia!AO26</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP26</f>
+        <v>0.71875</v>
       </c>
       <c r="H23" s="9" t="str">
-        <f>IF(Asistencia!AO26="","Sin datos",IF(Asistencia!AO26&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP26="","Sin datos",IF(Asistencia!AP26&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -6132,19 +6388,19 @@
         <v>124</v>
       </c>
       <c r="E24" s="13">
-        <f>Asistencia!AM27</f>
-        <v>22</v>
+        <f>Asistencia!AN27</f>
+        <v>23</v>
       </c>
       <c r="F24" s="14">
-        <f>Asistencia!AN27</f>
+        <f>Asistencia!AO27</f>
         <v>0</v>
       </c>
       <c r="G24" s="15">
-        <f>Asistencia!AO27</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP27</f>
+        <v>0.71875</v>
       </c>
       <c r="H24" s="16" t="str">
-        <f>IF(Asistencia!AO27="","Sin datos",IF(Asistencia!AO27&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP27="","Sin datos",IF(Asistencia!AP27&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -6162,19 +6418,19 @@
         <v>127</v>
       </c>
       <c r="E25" s="13">
-        <f>Asistencia!AM28</f>
-        <v>22</v>
+        <f>Asistencia!AN28</f>
+        <v>23</v>
       </c>
       <c r="F25" s="14">
-        <f>Asistencia!AN28</f>
+        <f>Asistencia!AO28</f>
         <v>0</v>
       </c>
       <c r="G25" s="15">
-        <f>Asistencia!AO28</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP28</f>
+        <v>0.71875</v>
       </c>
       <c r="H25" s="9" t="str">
-        <f>IF(Asistencia!AO28="","Sin datos",IF(Asistencia!AO28&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP28="","Sin datos",IF(Asistencia!AP28&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -6192,19 +6448,19 @@
         <v>130</v>
       </c>
       <c r="E26" s="13">
-        <f>Asistencia!AM29</f>
-        <v>22</v>
+        <f>Asistencia!AN29</f>
+        <v>23</v>
       </c>
       <c r="F26" s="14">
-        <f>Asistencia!AN29</f>
+        <f>Asistencia!AO29</f>
         <v>0</v>
       </c>
       <c r="G26" s="15">
-        <f>Asistencia!AO29</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP29</f>
+        <v>0.71875</v>
       </c>
       <c r="H26" s="16" t="str">
-        <f>IF(Asistencia!AO29="","Sin datos",IF(Asistencia!AO29&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP29="","Sin datos",IF(Asistencia!AP29&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -6222,19 +6478,19 @@
         <v>133</v>
       </c>
       <c r="E27" s="13">
-        <f>Asistencia!AM30</f>
-        <v>22</v>
+        <f>Asistencia!AN30</f>
+        <v>23</v>
       </c>
       <c r="F27" s="14">
-        <f>Asistencia!AN30</f>
+        <f>Asistencia!AO30</f>
         <v>0</v>
       </c>
       <c r="G27" s="15">
-        <f>Asistencia!AO30</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP30</f>
+        <v>0.71875</v>
       </c>
       <c r="H27" s="9" t="str">
-        <f>IF(Asistencia!AO30="","Sin datos",IF(Asistencia!AO30&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP30="","Sin datos",IF(Asistencia!AP30&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -6252,19 +6508,19 @@
         <v>136</v>
       </c>
       <c r="E28" s="13">
-        <f>Asistencia!AM31</f>
-        <v>22</v>
+        <f>Asistencia!AN31</f>
+        <v>23</v>
       </c>
       <c r="F28" s="14">
-        <f>Asistencia!AN31</f>
+        <f>Asistencia!AO31</f>
         <v>0</v>
       </c>
       <c r="G28" s="15">
-        <f>Asistencia!AO31</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP31</f>
+        <v>0.71875</v>
       </c>
       <c r="H28" s="16" t="str">
-        <f>IF(Asistencia!AO31="","Sin datos",IF(Asistencia!AO31&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP31="","Sin datos",IF(Asistencia!AP31&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -6282,19 +6538,19 @@
         <v>139</v>
       </c>
       <c r="E29" s="13">
-        <f>Asistencia!AM32</f>
-        <v>22</v>
+        <f>Asistencia!AN32</f>
+        <v>23</v>
       </c>
       <c r="F29" s="14">
-        <f>Asistencia!AN32</f>
+        <f>Asistencia!AO32</f>
         <v>0</v>
       </c>
       <c r="G29" s="15">
-        <f>Asistencia!AO32</f>
-        <v>0.6875</v>
+        <f>Asistencia!AP32</f>
+        <v>0.71875</v>
       </c>
       <c r="H29" s="9" t="str">
-        <f>IF(Asistencia!AO32="","Sin datos",IF(Asistencia!AO32&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AP32="","Sin datos",IF(Asistencia!AP32&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>

--- a/Administracion/Lista_Asistencia_ASS_CRN236396.xlsx
+++ b/Administracion/Lista_Asistencia_ASS_CRN236396.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\OneDrive\Documentos\GitHub\lc_arquitectura_de_sistemas_de_seguridad\Administracion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ddf5fb2bc65e958/Documentos/GitHub/lc_arquitectura_de_sistemas_de_seguridad/Administracion/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38376A8-59C5-44D7-8BA9-AC04E8A4A2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -1403,9 +1403,6 @@
     <xf numFmtId="0" fontId="14" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1419,6 +1416,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1742,96 +1742,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="49"/>
-      <c r="AM1" s="49"/>
-      <c r="AN1" s="49"/>
-      <c r="AO1" s="49"/>
-      <c r="AP1" s="49"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+      <c r="AB1" s="48"/>
+      <c r="AC1" s="48"/>
+      <c r="AD1" s="48"/>
+      <c r="AE1" s="48"/>
+      <c r="AF1" s="48"/>
+      <c r="AG1" s="48"/>
+      <c r="AH1" s="48"/>
+      <c r="AI1" s="48"/>
+      <c r="AJ1" s="48"/>
+      <c r="AK1" s="48"/>
+      <c r="AL1" s="48"/>
+      <c r="AM1" s="48"/>
+      <c r="AN1" s="48"/>
+      <c r="AO1" s="48"/>
+      <c r="AP1" s="48"/>
     </row>
     <row r="2" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="50"/>
-      <c r="AA2" s="50"/>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="50"/>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="50"/>
-      <c r="AG2" s="50"/>
-      <c r="AH2" s="50"/>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="50"/>
-      <c r="AK2" s="50"/>
-      <c r="AL2" s="50"/>
-      <c r="AM2" s="50"/>
-      <c r="AN2" s="50"/>
-      <c r="AO2" s="50"/>
-      <c r="AP2" s="50"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="49"/>
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="49"/>
+      <c r="AF2" s="49"/>
+      <c r="AG2" s="49"/>
+      <c r="AH2" s="49"/>
+      <c r="AI2" s="49"/>
+      <c r="AJ2" s="49"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
+      <c r="AM2" s="49"/>
+      <c r="AN2" s="49"/>
+      <c r="AO2" s="49"/>
+      <c r="AP2" s="49"/>
     </row>
     <row r="3" spans="1:42" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1855,70 +1855,70 @@
       <c r="G3" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="46" t="s">
+      <c r="I3" s="50"/>
+      <c r="J3" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="46"/>
-      <c r="L3" s="45" t="s">
+      <c r="K3" s="45"/>
+      <c r="L3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="45"/>
-      <c r="N3" s="46" t="s">
+      <c r="M3" s="50"/>
+      <c r="N3" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="46"/>
-      <c r="P3" s="45" t="s">
+      <c r="O3" s="45"/>
+      <c r="P3" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="46" t="s">
+      <c r="Q3" s="50"/>
+      <c r="R3" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="S3" s="46"/>
-      <c r="T3" s="45" t="s">
+      <c r="S3" s="45"/>
+      <c r="T3" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="U3" s="45"/>
-      <c r="V3" s="46" t="s">
+      <c r="U3" s="50"/>
+      <c r="V3" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="W3" s="46"/>
-      <c r="X3" s="45" t="s">
+      <c r="W3" s="45"/>
+      <c r="X3" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="46" t="s">
+      <c r="Y3" s="50"/>
+      <c r="Z3" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="45" t="s">
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="46" t="s">
+      <c r="AC3" s="50"/>
+      <c r="AD3" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="AE3" s="46"/>
-      <c r="AF3" s="45" t="s">
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="AG3" s="45"/>
-      <c r="AH3" s="46" t="s">
+      <c r="AG3" s="50"/>
+      <c r="AH3" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="AI3" s="46"/>
-      <c r="AJ3" s="45" t="s">
+      <c r="AI3" s="45"/>
+      <c r="AJ3" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="AK3" s="45"/>
-      <c r="AL3" s="46" t="s">
+      <c r="AK3" s="50"/>
+      <c r="AL3" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="46"/>
+      <c r="AM3" s="45"/>
       <c r="AN3" s="4" t="s">
         <v>22</v>
       </c>
@@ -5464,12 +5464,12 @@
       </c>
     </row>
     <row r="33" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="47" t="s">
+      <c r="A33" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="B33" s="47"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -5606,50 +5606,50 @@
       <c r="AP33" s="5"/>
     </row>
     <row r="34" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="48" t="s">
+      <c r="A34" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="B34" s="48"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="48"/>
-      <c r="K34" s="48"/>
-      <c r="L34" s="48"/>
-      <c r="M34" s="48"/>
-      <c r="N34" s="48"/>
-      <c r="O34" s="48"/>
-      <c r="P34" s="48"/>
-      <c r="Q34" s="48"/>
-      <c r="R34" s="48"/>
-      <c r="S34" s="48"/>
-      <c r="T34" s="48"/>
-      <c r="U34" s="48"/>
-      <c r="V34" s="48"/>
-      <c r="W34" s="48"/>
-      <c r="X34" s="48"/>
-      <c r="Y34" s="48"/>
-      <c r="Z34" s="48"/>
-      <c r="AA34" s="48"/>
-      <c r="AB34" s="48"/>
-      <c r="AC34" s="48"/>
-      <c r="AD34" s="48"/>
-      <c r="AE34" s="48"/>
-      <c r="AF34" s="48"/>
-      <c r="AG34" s="48"/>
-      <c r="AH34" s="48"/>
-      <c r="AI34" s="48"/>
-      <c r="AJ34" s="48"/>
-      <c r="AK34" s="48"/>
-      <c r="AL34" s="48"/>
-      <c r="AM34" s="48"/>
-      <c r="AN34" s="48"/>
-      <c r="AO34" s="48"/>
-      <c r="AP34" s="48"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="47"/>
+      <c r="K34" s="47"/>
+      <c r="L34" s="47"/>
+      <c r="M34" s="47"/>
+      <c r="N34" s="47"/>
+      <c r="O34" s="47"/>
+      <c r="P34" s="47"/>
+      <c r="Q34" s="47"/>
+      <c r="R34" s="47"/>
+      <c r="S34" s="47"/>
+      <c r="T34" s="47"/>
+      <c r="U34" s="47"/>
+      <c r="V34" s="47"/>
+      <c r="W34" s="47"/>
+      <c r="X34" s="47"/>
+      <c r="Y34" s="47"/>
+      <c r="Z34" s="47"/>
+      <c r="AA34" s="47"/>
+      <c r="AB34" s="47"/>
+      <c r="AC34" s="47"/>
+      <c r="AD34" s="47"/>
+      <c r="AE34" s="47"/>
+      <c r="AF34" s="47"/>
+      <c r="AG34" s="47"/>
+      <c r="AH34" s="47"/>
+      <c r="AI34" s="47"/>
+      <c r="AJ34" s="47"/>
+      <c r="AK34" s="47"/>
+      <c r="AL34" s="47"/>
+      <c r="AM34" s="47"/>
+      <c r="AN34" s="47"/>
+      <c r="AO34" s="47"/>
+      <c r="AP34" s="47"/>
     </row>
     <row r="35" spans="1:42" x14ac:dyDescent="0.25">
       <c r="AH35" s="26" t="s">
@@ -5658,6 +5658,10 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AJ3:AK3"/>
     <mergeCell ref="AL3:AM3"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A34:AP34"/>
@@ -5674,10 +5678,6 @@
     <mergeCell ref="X3:Y3"/>
     <mergeCell ref="Z3:AA3"/>
     <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AJ3:AK3"/>
   </mergeCells>
   <conditionalFormatting sqref="AP6:AP32">
     <cfRule type="expression" dxfId="1" priority="2">
@@ -5707,16 +5707,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
